--- a/attendanceHelper/计原25石老师班名单demo.xlsx
+++ b/attendanceHelper/计原25石老师班名单demo.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\Projects\attendanceHelper\attendanceHelper\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903644F4-9B47-407A-A980-FD68BCC0E1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9830" yWindow="2280" windowWidth="12660" windowHeight="13000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9830" yWindow="2280" windowWidth="12660" windowHeight="13000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,82 +16,82 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
-    <t>姓名</t>
-  </si>
-  <si>
-    <t>2025-09-16</t>
-  </si>
-  <si>
-    <t>2025-09-23</t>
-  </si>
-  <si>
-    <t>2025-09-30</t>
-  </si>
-  <si>
-    <t>2025-10-07</t>
-  </si>
-  <si>
-    <t>2025-10-14</t>
-  </si>
-  <si>
-    <t>2025-10-21</t>
-  </si>
-  <si>
-    <t>2025-10-28</t>
-  </si>
-  <si>
-    <t>2025-11-04</t>
-  </si>
-  <si>
-    <t>2025-11-11</t>
-  </si>
-  <si>
-    <t>2025-11-18</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>王宇鹏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>史家祺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>曹慕凡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>胡飞羽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>蔡灿</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>杨非凡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵紫彤</t>
+    <t xml:space="preserve">姓名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">王宇鹏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">史家祺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">曹慕凡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">胡飞羽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">蔡灿</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">杨非凡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">赵紫彤</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -105,6 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -162,7 +157,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -176,11 +171,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -409,7 +404,7 @@
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
-          <a:sp3d>
+          <a:sp3d prstMaterial="warmMatte">
             <a:bevelT w="63500" h="25400"/>
           </a:sp3d>
         </a:effectStyle>
@@ -472,7 +467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -533,35 +528,56 @@
       <c r="A2" t="s">
         <v>17</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/attendanceHelper/计原25石老师班名单demo.xlsx
+++ b/attendanceHelper/计原25石老师班名单demo.xlsx
@@ -561,7 +561,7 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">

--- a/attendanceHelper/计原25石老师班名单demo.xlsx
+++ b/attendanceHelper/计原25石老师班名单demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="9830" yWindow="2280" windowWidth="12660" windowHeight="13000"/>
+    <workbookView xWindow="7070" yWindow="2280" windowWidth="12660" windowHeight="13000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -561,7 +561,7 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -569,7 +569,7 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">

--- a/attendanceHelper/计原25石老师班名单demo.xlsx
+++ b/attendanceHelper/计原25石老师班名单demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="7070" yWindow="2280" windowWidth="12660" windowHeight="13000"/>
+    <workbookView xWindow="4520" yWindow="2180" windowWidth="12660" windowHeight="13000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -531,6 +531,9 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -539,6 +542,9 @@
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -547,6 +553,9 @@
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -555,6 +564,9 @@
       <c r="B5">
         <v>1</v>
       </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -563,6 +575,9 @@
       <c r="B6">
         <v>1</v>
       </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -571,12 +586,18 @@
       <c r="B7">
         <v>0</v>
       </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <v>1</v>
       </c>
     </row>
